--- a/naver-place-crawler/results_derma/일산_피부과.xlsx
+++ b/naver-place-crawler/results_derma/일산_피부과.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스타필의원</t>
+          <t>예쁨톡톡의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>miandmo@naver.com</t>
+          <t>seasons0907@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-965-2255</t>
+          <t>031-943-5422</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 호국로789번길 6 중앙빌딩 3층</t>
+          <t>경기도 파주시 초롱꽃로 109 4층 407호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miandmo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>277</v>
+        <v>219</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20367149</t>
+          <t>1919348740</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20367149</t>
+          <t>https://m.place.naver.com/place/1919348740</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스카이비뇨의학과의원</t>
+          <t>더히엘의원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>skyuroskin@naver.com</t>
+          <t>thehielclinic@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-813-7582</t>
+          <t>0507-1490-7910</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을1로 73 신성메디칼타운 601호</t>
+          <t>경기도 고양시 일산동구 위시티로 34 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skyuroskin</t>
+          <t>https://blog.naver.com/thehielclinic</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>412</v>
+        <v>275</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="R3" t="n">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1050410147</t>
+          <t>1282180214</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050410147</t>
+          <t>https://m.place.naver.com/place/1282180214</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,44 +752,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>앤유의원</t>
+          <t>뷰티안의원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>relized71026@naver.com</t>
+          <t>objms@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1359-2994</t>
+          <t>0507-1396-2816</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 55 효산캐슬빌딩 4층</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타D 221호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://nuclinic.co.kr/</t>
+          <t>https://blog.naver.com/objms</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>554</v>
+        <v>12</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1109875670</t>
+          <t>1398931993</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109875670</t>
+          <t>https://m.place.naver.com/place/1398931993</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리뉴앤영의원</t>
+          <t>미소가인피부과의원 일산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>twitchy378386@naver.com</t>
+          <t>misogainep@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1355-2651</t>
+          <t>031-901-7603</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-9 레이크프라자2, 5층</t>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.renew-young.com/</t>
+          <t>http://www.misogain.co.kr/is/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -894,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>880</v>
+        <v>201</v>
       </c>
       <c r="Q5" t="n">
-        <v>216</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>1096</v>
+        <v>212</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1463393218</t>
+          <t>13139640</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463393218</t>
+          <t>https://m.place.naver.com/place/13139640</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더드림의원 일산</t>
+          <t>사적인 아름다움 지유의원 일산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>micketionath53857@naver.com</t>
+          <t>rkawjs1891@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1307-7365</t>
+          <t>031-812-0196</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 4층</t>
+          <t>경기도 고양시 일산동구 정발산로 21 501호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://thedreamskin.co.kr</t>
+          <t>https://ilsan.gu.clinic/kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>749</v>
+        <v>3359</v>
       </c>
       <c r="Q6" t="n">
-        <v>437</v>
+        <v>3037</v>
       </c>
       <c r="R6" t="n">
-        <v>1186</v>
+        <v>6396</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1178991103</t>
+          <t>1686302028</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178991103</t>
+          <t>https://m.place.naver.com/place/1686302028</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>봄날초이스의원</t>
+          <t>옐로우의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bomnalp@naver.com</t>
+          <t>heesunvly0826@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1418-0888</t>
+          <t>031-907-6111</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 후곡로 22 신일빌딩 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://bomnals.co.kr</t>
+          <t>http://www.yellowclinic.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>794</v>
+        <v>217</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>707</v>
       </c>
       <c r="R7" t="n">
-        <v>798</v>
+        <v>924</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11597476</t>
+          <t>32047077</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11597476</t>
+          <t>https://m.place.naver.com/place/32047077</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,44 +1128,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>파크뷰의원 운정점</t>
+          <t>일산의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>thdwjdals25@naver.com</t>
+          <t>medi114_official@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-939-1100</t>
+          <t>031-976-1240</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 507 월드타워9차 6층</t>
+          <t>경기도 고양시 일산서구 고양대로 691</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pskin.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1139</v>
+        <v>205</v>
       </c>
       <c r="Q8" t="n">
-        <v>1961</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>3100</v>
+        <v>207</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>33021543</t>
+          <t>13237890</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33021543</t>
+          <t>https://m.place.naver.com/place/13237890</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>최병문피부과의원</t>
+          <t>위시티아름다운의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cleanz77@naver.com</t>
+          <t>wicitybeauty@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-965-5800</t>
+          <t>031-962-5350</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 호국로 787 원당메디컬프라자</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워 3층 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wicitybeauty</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>976</v>
+        <v>190</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>994</v>
+        <v>195</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13237675</t>
+          <t>1707720691</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237675</t>
+          <t>https://m.place.naver.com/place/1707720691</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>메디누리미의원</t>
+          <t>스무살의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>drkwun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-915-7577</t>
+          <t>031-932-9737</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 53</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://smoothall.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,22 +1364,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>124</v>
+        <v>691</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>281</v>
       </c>
       <c r="R10" t="n">
-        <v>127</v>
+        <v>972</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35418720</t>
+          <t>31310223</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35418720</t>
+          <t>https://m.place.naver.com/place/31310223</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,39 +1410,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>내안에봄의원 일산</t>
+          <t>리뉴앤영의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>naeanebom@naver.com</t>
+          <t>twitchy378386@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1391-8576</t>
+          <t>0507-1355-2651</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 33 벨라시타 쇼핑몰 1층 1102호 내안에봄의원 일산</t>
+          <t>경기도 고양시 일산동구 정발산로 31-9 레이크프라자2, 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/@pibuunnie</t>
+          <t>https://www.renew-young.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>650</v>
+        <v>887</v>
       </c>
       <c r="Q11" t="n">
-        <v>1505</v>
+        <v>217</v>
       </c>
       <c r="R11" t="n">
-        <v>2155</v>
+        <v>1104</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13584814</t>
+          <t>1463393218</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13584814</t>
+          <t>https://m.place.naver.com/place/1463393218</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,39 +1504,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>웰스피부과의원</t>
+          <t>레이퀸의원</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wellspaju123@naver.com</t>
+          <t>islaqueen@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-943-2374</t>
+          <t>0507-1448-1256</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 133 형성프라자 3층</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 219호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.wellsclinicpaju.co.kr/</t>
+          <t>https://blog.naver.com/islaqueen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1552,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>543</v>
+        <v>149</v>
       </c>
       <c r="Q12" t="n">
-        <v>170</v>
+        <v>943</v>
       </c>
       <c r="R12" t="n">
-        <v>713</v>
+        <v>1092</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1941007069</t>
+          <t>1117977850</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941007069</t>
+          <t>https://m.place.naver.com/place/1117977850</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,33 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>유앤아이의원 일산점</t>
+          <t>데일리즈의원 일산</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>chiritachi197244@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+          <t>ldsmhan@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>031-994-6021</t>
+          <t>031-907-5400</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 38-5 이레21빌딩 4층 401, 402, 403호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 일산라페스타 E동 5층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.isuni114.co.kr/</t>
+          <t>http://dailys.co.kr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1634,12 +1630,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1659,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>803</v>
+        <v>245</v>
       </c>
       <c r="Q13" t="n">
-        <v>4875</v>
+        <v>1456</v>
       </c>
       <c r="R13" t="n">
-        <v>5678</v>
+        <v>1701</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1674,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1143822491</t>
+          <t>13432168</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1143822491</t>
+          <t>https://m.place.naver.com/place/13432168</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1696,34 +1692,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>사적인 아름다움 지유의원 일산점</t>
+          <t>스카이비뇨의학과의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rkawjs1891@naver.com</t>
+          <t>skyuroskin@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>031-812-0196</t>
+          <t>031-813-7582</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 21 501호</t>
+          <t>경기도 고양시 일산동구 숲속마을1로 73 신성메디칼타운 601호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://ilsan.gu.clinic/kr</t>
+          <t>https://blog.naver.com/skyuroskin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1733,7 +1729,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1749,17 +1745,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3335</v>
+        <v>412</v>
       </c>
       <c r="Q14" t="n">
-        <v>3113</v>
+        <v>31</v>
       </c>
       <c r="R14" t="n">
-        <v>6448</v>
+        <v>443</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1768,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1686302028</t>
+          <t>1050410147</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1686302028</t>
+          <t>https://m.place.naver.com/place/1050410147</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1790,39 +1786,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>하얀나라김피부과의원</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>imagine77-@naver.com</t>
-        </is>
-      </c>
+          <t>일산비타민의원</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>031-917-7588</t>
+          <t>0507-1406-2040</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 576 대성프라자</t>
+          <t>경기도 고양시 일산서구 중앙로 1426 일송노브레스</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://www.laser2u.com/</t>
+          <t>http://www.vitaminskin.kr/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1847,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1303</v>
+        <v>529</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1317</v>
+        <v>535</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1862,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>11535528</t>
+          <t>12776782</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11535528</t>
+          <t>https://m.place.naver.com/place/12776782</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1884,24 +1876,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>유진피부과의원</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>d0ig-785m6a@naver.com</t>
-        </is>
-      </c>
+          <t>주엽 제일의원</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>031-917-6749</t>
+          <t>031-918-8118</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강선로 59 동신파크빌딩</t>
+          <t>경기도 고양시 일산서구 중앙로 1437 화성프라자</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1941,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>516</v>
+        <v>173</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>522</v>
+        <v>173</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1956,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13237201</t>
+          <t>13237231</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237201</t>
+          <t>https://m.place.naver.com/place/13237231</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1978,34 +1966,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>베스트미의원</t>
+          <t>닥터에버스의원 일산</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bestme2002@naver.com</t>
+          <t>lavender_koko@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>031-907-3375</t>
+          <t>0507-1431-2093</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 229 글로리코아 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티빌딩 3층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://evers5.co.kr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2015,7 +2003,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2026,22 +2014,22 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>167</v>
+        <v>889</v>
       </c>
       <c r="Q17" t="n">
-        <v>110</v>
+        <v>2381</v>
       </c>
       <c r="R17" t="n">
-        <v>277</v>
+        <v>3270</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2050,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1084521027</t>
+          <t>1023579945</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084521027</t>
+          <t>https://m.place.naver.com/place/1023579945</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2072,34 +2060,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>더히엘의원</t>
+          <t>산타클로스의원 일산점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>thehielclinic@naver.com</t>
+          <t>sjwgroup0827@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1490-7910</t>
+          <t>031-905-7591</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 34 3층</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 55 산타클로스의원</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thehielclinic</t>
+          <t>http://www.santaskin.co.kr/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2109,7 +2097,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2120,22 +2108,22 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>272</v>
       </c>
       <c r="Q18" t="n">
-        <v>160</v>
+        <v>483</v>
       </c>
       <c r="R18" t="n">
-        <v>432</v>
+        <v>755</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2144,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1282180214</t>
+          <t>13315650</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282180214</t>
+          <t>https://m.place.naver.com/place/13315650</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2166,34 +2154,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>다시봄날의원 파주점</t>
+          <t>고은미래의원 일산점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>springdayclinic22@naver.com</t>
+          <t>go9037600@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1468-7666</t>
+          <t>0507-1380-7601</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1074 삼융시네마 405호</t>
+          <t>경기도 고양시 일산동구 숲속마을로 22 진넥스블루오션 2층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://pj.springdayclinic.com/</t>
+          <t>https://blog.naver.com/go9037600</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2214,22 +2202,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>857</v>
+        <v>534</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="R19" t="n">
-        <v>867</v>
+        <v>738</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2238,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1800857823</t>
+          <t>1770208123</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800857823</t>
+          <t>https://m.place.naver.com/place/1770208123</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2260,29 +2248,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VS라인의원 일산점</t>
+          <t>파크뷰의원 운정점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vsline_official@naver.com</t>
+          <t>thdwjdals25@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1498-7031</t>
+          <t>031-939-1100</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 3층 301호</t>
+          <t>경기도 파주시 와석순환로 507 월드타워9차 6층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://is.vsline.kr/</t>
+          <t>http://pskin.kr/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2292,12 +2280,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2317,13 +2305,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1723</v>
+        <v>1139</v>
       </c>
       <c r="Q20" t="n">
-        <v>8184</v>
+        <v>1959</v>
       </c>
       <c r="R20" t="n">
-        <v>9907</v>
+        <v>3098</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2332,17 +2320,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1245507452</t>
+          <t>33021543</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245507452</t>
+          <t>https://m.place.naver.com/place/33021543</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2354,29 +2342,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>오킴스피부과의원</t>
+          <t>제너리스의원 일산</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>sgygag98@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1481-9335</t>
+          <t>031-904-9555</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 123 뉴삼창빌딩 10층</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HxbKpC</t>
+          <t>https://is.generless.com</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,17 +2395,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>917</v>
+        <v>1488</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>7344</v>
       </c>
       <c r="R21" t="n">
-        <v>951</v>
+        <v>8832</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2426,17 +2414,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12776434</t>
+          <t>1266922390</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12776434</t>
+          <t>https://m.place.naver.com/place/1266922390</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2448,39 +2436,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>고은미래의원 일산점</t>
+          <t>유노라의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>go9037600@naver.com</t>
+          <t>vivaclinic@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1380-7601</t>
+          <t>031-923-7774</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 22 진넥스블루오션 2층</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 GIFC 오피스동 4층 403호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/go9037600</t>
+          <t>https://www.eunoraclinic.com</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2496,22 +2484,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>534</v>
+        <v>729</v>
       </c>
       <c r="Q22" t="n">
-        <v>203</v>
+        <v>576</v>
       </c>
       <c r="R22" t="n">
-        <v>737</v>
+        <v>1305</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2520,17 +2508,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1770208123</t>
+          <t>1267159783</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1770208123</t>
+          <t>https://m.place.naver.com/place/1267159783</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2542,39 +2530,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>포레의원</t>
+          <t>리버스의원 일산</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>foreverilsan1@naver.com</t>
+          <t>dbsvlfwns1@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1309-8352</t>
+          <t>0507-1429-5556</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 38 401~402호</t>
+          <t>경기도 고양시 일산동구 정발산로 23 호수빌딩 502호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://ilsanfore.co.kr</t>
+          <t>https://is.reverseclinic.com</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2595,17 +2583,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>277</v>
+        <v>752</v>
       </c>
       <c r="Q23" t="n">
-        <v>49</v>
+        <v>2254</v>
       </c>
       <c r="R23" t="n">
-        <v>326</v>
+        <v>3006</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2614,17 +2602,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1596281549</t>
+          <t>34508126</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596281549</t>
+          <t>https://m.place.naver.com/place/34508126</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2636,39 +2624,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>김영숙피부과의원</t>
+          <t>일산고운세상피부과의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dermakims@naver.com</t>
+          <t>gwssskin@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>031-901-3133</t>
+          <t>031-932-8275</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1124 이마트 2층 김영숙피부과</t>
+          <t>경기도 고양시 일산동구 정발산로 47 웅신아트 4층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.skinkim.net/</t>
+          <t>http://www.gowoonss.com/ilsan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2684,7 +2672,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2693,13 +2681,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1960</v>
+        <v>396</v>
       </c>
       <c r="Q24" t="n">
-        <v>289</v>
+        <v>633</v>
       </c>
       <c r="R24" t="n">
-        <v>2249</v>
+        <v>1029</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2708,17 +2696,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13236932</t>
+          <t>13096274</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13236932</t>
+          <t>https://m.place.naver.com/place/13096274</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2730,29 +2718,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>루체피부과의원</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>luceskin11@naver.com</t>
-        </is>
-      </c>
+          <t>블리비의원 일산점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>031-917-8088</t>
+          <t>1833-7382</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1444 태원빌딩 4층</t>
+          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티 2층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.luce-skin.com/</t>
+          <t>http://www.velyb.kr</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2787,13 +2771,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>418</v>
+        <v>5990</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>4685</v>
       </c>
       <c r="R25" t="n">
-        <v>442</v>
+        <v>10675</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2802,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11531592</t>
+          <t>1592961756</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11531592</t>
+          <t>https://m.place.naver.com/place/1592961756</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2824,34 +2808,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>일산의원</t>
+          <t>톤즈의원 일산</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>medi114_official@naver.com</t>
+          <t>dpilsan@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>031-976-1240</t>
+          <t>0507-1329-1753</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 691</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 61 4층 톤즈의원 일산</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://tonesclinic.co.kr/ilsan</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2861,7 +2845,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2872,22 +2856,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>205</v>
+        <v>4292</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>5509</v>
       </c>
       <c r="R26" t="n">
-        <v>207</v>
+        <v>9801</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2896,17 +2880,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13237890</t>
+          <t>1053186040</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237890</t>
+          <t>https://m.place.naver.com/place/1053186040</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2918,29 +2902,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>유노라의원</t>
+          <t>웰스피부과의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>vivaclinic@naver.com</t>
+          <t>wellspaju123@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-923-7774</t>
+          <t>031-943-2374</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 GIFC 오피스동 4층 403호</t>
+          <t>경기도 파주시 와석순환로 133 형성프라자 3층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.eunoraclinic.com</t>
+          <t>https://www.wellsclinicpaju.co.kr/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2971,17 +2955,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>728</v>
+        <v>544</v>
       </c>
       <c r="Q27" t="n">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c r="R27" t="n">
-        <v>1325</v>
+        <v>718</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2990,17 +2974,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1267159783</t>
+          <t>1941007069</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267159783</t>
+          <t>https://m.place.naver.com/place/1941007069</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3012,34 +2996,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>일산차앤박피부과의원</t>
+          <t>봄날초이스의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ilsan_cnp@naver.com</t>
+          <t>bomnalp@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>031-911-7571</t>
+          <t>0507-1418-0888</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1441 하나은행 건물 5층</t>
+          <t>경기도 고양시 일산서구 후곡로 22 신일빌딩 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://ilsancnp.com/</t>
+          <t>http://bomnals.co.kr</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3060,7 +3044,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3069,13 +3053,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>384</v>
+        <v>794</v>
       </c>
       <c r="Q28" t="n">
-        <v>667</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1051</v>
+        <v>798</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3084,17 +3068,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>32528322</t>
+          <t>11597476</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32528322</t>
+          <t>https://m.place.naver.com/place/11597476</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3106,29 +3090,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>톤즈의원 일산</t>
+          <t>밴스의원 일산</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dpilsan@naver.com</t>
+          <t>vandsis@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1329-1753</t>
+          <t>031-994-0380</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 61 4층 톤즈의원 일산</t>
+          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 6층 601, 603호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://tonesclinic.co.kr/ilsan</t>
+          <t>https://ilsan.vandsclinic.co.kr/?channel=1687</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3163,13 +3147,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4244</v>
+        <v>1386</v>
       </c>
       <c r="Q29" t="n">
-        <v>5500</v>
+        <v>3542</v>
       </c>
       <c r="R29" t="n">
-        <v>9744</v>
+        <v>4928</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3178,17 +3162,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1053186040</t>
+          <t>1481200696</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053186040</t>
+          <t>https://m.place.naver.com/place/1481200696</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3200,29 +3184,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>블리비의원 일산점</t>
+          <t>유진피부과의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sahibswan@naver.com</t>
+          <t>d0ig-785m6a@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1833-7382</t>
+          <t>031-917-6749</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티 2층</t>
+          <t>경기도 고양시 일산서구 강선로 59 동신파크빌딩</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.velyb.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3232,7 +3216,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3257,13 +3241,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5945</v>
+        <v>517</v>
       </c>
       <c r="Q30" t="n">
-        <v>4624</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>10569</v>
+        <v>523</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3272,17 +3256,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1592961756</t>
+          <t>13237201</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1592961756</t>
+          <t>https://m.place.naver.com/place/13237201</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3294,29 +3278,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>스무살의원</t>
+          <t>메디누리미의원</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>drkwun@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-932-9737</t>
+          <t>031-915-7577</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔1</t>
+          <t>경기도 고양시 일산서구 일현로 53</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://smoothall.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3326,12 +3310,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3342,22 +3326,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>668</v>
+        <v>124</v>
       </c>
       <c r="Q31" t="n">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>947</v>
+        <v>127</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3366,17 +3350,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>31310223</t>
+          <t>35418720</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31310223</t>
+          <t>https://m.place.naver.com/place/35418720</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3388,48 +3372,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>미앤미의원 일산</t>
+          <t>일산차앤박피부과의원</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abte1954@naver.com</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>webtick@gmail.com</t>
-        </is>
-      </c>
+          <t>ilsan_cnp@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1411-8941</t>
+          <t>031-911-7571</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 8층 미앤미의원 일산</t>
+          <t>경기도 고양시 일산서구 중앙로 1441 하나은행 건물 5층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://is.mipretty.co.kr/</t>
+          <t>http://ilsancnp.com/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3445,17 +3425,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>561</v>
+        <v>386</v>
       </c>
       <c r="Q32" t="n">
-        <v>4186</v>
+        <v>667</v>
       </c>
       <c r="R32" t="n">
-        <v>4747</v>
+        <v>1053</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3464,17 +3444,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>35135661</t>
+          <t>32528322</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35135661</t>
+          <t>https://m.place.naver.com/place/32528322</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3486,34 +3466,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>밴스의원 일산</t>
+          <t>원피부과의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>vandsis@naver.com</t>
+          <t>beanb1n@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>031-994-0380</t>
+          <t>031-904-0319</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 6층 601, 603호</t>
+          <t>경기도 고양시 일산동구 강송로 179 신일산크리닉 401호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://ilsan.vandsclinic.co.kr/?channel=1687</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3523,7 +3503,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3534,22 +3514,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1382</v>
+        <v>379</v>
       </c>
       <c r="Q33" t="n">
-        <v>3663</v>
+        <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>5045</v>
+        <v>387</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3558,17 +3538,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1481200696</t>
+          <t>11867907</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481200696</t>
+          <t>https://m.place.naver.com/place/11867907</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3580,29 +3560,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>스노우의원 파주운정점</t>
+          <t>하얀나라김피부과의원</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>allbaro@naver.com</t>
+          <t>imagine77-@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1410-0913</t>
+          <t>031-917-7588</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1246 유은타워8차 2층 201호~205호</t>
+          <t>경기도 고양시 일산서구 일산로 576 대성프라자</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://paju-snow.co.kr/</t>
+          <t>http://www.laser2u.com/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3617,7 +3597,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3628,22 +3608,22 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1346</v>
+        <v>1303</v>
       </c>
       <c r="Q34" t="n">
-        <v>343</v>
+        <v>14</v>
       </c>
       <c r="R34" t="n">
-        <v>1689</v>
+        <v>1317</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3652,17 +3632,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1338314528</t>
+          <t>11535528</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338314528</t>
+          <t>https://m.place.naver.com/place/11535528</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3674,34 +3654,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>일산고운세상피부과의원</t>
+          <t>루미엘의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gwssskin@naver.com</t>
+          <t>cliniclumiere@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>031-932-8275</t>
+          <t>0507-1350-6971</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 웅신아트 4층</t>
+          <t>경기도 파주시 와석순환로515번길 91 프라임타워 6층 607호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://www.gowoonss.com/ilsan</t>
+          <t>https://cliniclumiere.com/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3731,13 +3711,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="Q35" t="n">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="R35" t="n">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3746,17 +3726,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>13096274</t>
+          <t>1267511624</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13096274</t>
+          <t>https://m.place.naver.com/place/1267511624</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3768,29 +3748,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>일산주엽 톡스앤필의원</t>
+          <t>루체피부과의원</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ilsantox@naver.com</t>
+          <t>luceskin11@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>031-994-0188</t>
+          <t>031-917-8088</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1413 동영빌딩 3층</t>
+          <t>경기도 고양시 일산서구 중앙로 1444 태원빌딩 4층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ilsantox</t>
+          <t>http://www.luce-skin.com/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3805,7 +3785,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3821,17 +3801,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1158</v>
+        <v>418</v>
       </c>
       <c r="Q36" t="n">
-        <v>1973</v>
+        <v>24</v>
       </c>
       <c r="R36" t="n">
-        <v>3131</v>
+        <v>442</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3840,17 +3820,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1386191168</t>
+          <t>11531592</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386191168</t>
+          <t>https://m.place.naver.com/place/11531592</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3862,34 +3842,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>뷰티안의원</t>
+          <t>더드림의원 일산</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>objms@naver.com</t>
+          <t>micketionath53857@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1396-2816</t>
+          <t>0507-1307-7365</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타D 221호</t>
+          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 4층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/objms</t>
+          <t>http://thedreamskin.co.kr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3910,7 +3890,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3919,13 +3899,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>748</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="R37" t="n">
-        <v>11</v>
+        <v>1185</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3934,17 +3914,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1398931993</t>
+          <t>1178991103</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1398931993</t>
+          <t>https://m.place.naver.com/place/1178991103</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3956,29 +3936,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>온봄의원</t>
+          <t>김영숙피부과의원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>onbom_clinic@naver.com</t>
+          <t>dermakims@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1323-0075</t>
+          <t>031-901-3133</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 45 C동 2층 218호</t>
+          <t>경기도 고양시 일산동구 중앙로 1124 이마트 2층 김영숙피부과</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://www.onbomclinic.co.kr</t>
+          <t>http://www.skinkim.net/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3988,12 +3968,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4009,17 +3989,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>249</v>
+        <v>1960</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="R38" t="n">
-        <v>278</v>
+        <v>2249</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4028,17 +4008,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1303562689</t>
+          <t>13236932</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303562689</t>
+          <t>https://m.place.naver.com/place/13236932</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4050,33 +4030,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>메이린의원 일산</t>
+          <t>앤유의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>alawpearson@naver.com</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>mkt@maylin.co.kr</t>
-        </is>
-      </c>
+          <t>relized71026@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1393-0000</t>
+          <t>0507-1359-2994</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 현대백화점 킨텍스점 9층 메이린클리닉</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 55 효산캐슬빌딩 4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.maylin.co.kr/ilsan/</t>
+          <t>http://nuclinic.co.kr/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4091,7 +4067,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4111,13 +4087,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="Q39" t="n">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="R39" t="n">
-        <v>409</v>
+        <v>557</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4126,17 +4102,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>19534963</t>
+          <t>1109875670</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19534963</t>
+          <t>https://m.place.naver.com/place/1109875670</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4148,34 +4124,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>위시티아름다운의원</t>
+          <t>다시봄날의원 파주점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>wicitybeauty@naver.com</t>
+          <t>springdayclinic22@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>031-962-5350</t>
+          <t>0507-1468-7666</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워 3층 302호</t>
+          <t>경기도 파주시 경의로 1074 삼융시네마 405호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wicitybeauty</t>
+          <t>https://pj.springdayclinic.com/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4196,22 +4172,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>190</v>
+        <v>872</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R40" t="n">
-        <v>195</v>
+        <v>882</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4220,17 +4196,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1707720691</t>
+          <t>1800857823</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707720691</t>
+          <t>https://m.place.naver.com/place/1800857823</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4242,34 +4218,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>루미엘의원</t>
+          <t>엘로디의원 파주운정본점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cliniclumiere@naver.com</t>
+          <t>elodieclinic@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1350-6971</t>
+          <t>0507-1372-8712</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로515번길 91 프라임타워 6층 607호</t>
+          <t>경기도 파주시 경의로 1204 월드타워10 4층 405호~410호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://cliniclumiere.com/</t>
+          <t>https://blog.naver.com/elodieclinic</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4290,22 +4266,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>360</v>
+        <v>1051</v>
       </c>
       <c r="Q41" t="n">
-        <v>723</v>
+        <v>1596</v>
       </c>
       <c r="R41" t="n">
-        <v>1083</v>
+        <v>2647</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4314,17 +4290,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1267511624</t>
+          <t>1637191468</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267511624</t>
+          <t>https://m.place.naver.com/place/1637191468</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4336,29 +4312,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>제너리스의원 일산</t>
+          <t>아비쥬의원 일산</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sgygag98@naver.com</t>
+          <t>abijou0@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>031-904-9555</t>
+          <t>1544-0377</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 4층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 64 홈플러스 일산점 4층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://is.generless.com</t>
+          <t>http://www.abijouclinicis.com</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4368,12 +4344,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4393,13 +4369,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1483</v>
+        <v>4774</v>
       </c>
       <c r="Q42" t="n">
-        <v>6765</v>
+        <v>2140</v>
       </c>
       <c r="R42" t="n">
-        <v>8248</v>
+        <v>6914</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4408,17 +4384,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1266922390</t>
+          <t>1229474688</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266922390</t>
+          <t>https://m.place.naver.com/place/1229474688</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4430,39 +4406,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아비쥬의원 일산</t>
+          <t>일산주엽 톡스앤필의원</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abijou0@naver.com</t>
+          <t>ilsantox@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1544-0377</t>
+          <t>031-994-0188</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 64 홈플러스 일산점 4층</t>
+          <t>경기도 고양시 일산서구 중앙로 1413 동영빌딩 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.abijouclinicis.com</t>
+          <t>https://blog.naver.com/ilsantox</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4478,7 +4454,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4487,13 +4463,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4765</v>
+        <v>1186</v>
       </c>
       <c r="Q43" t="n">
-        <v>1966</v>
+        <v>2080</v>
       </c>
       <c r="R43" t="n">
-        <v>6731</v>
+        <v>3266</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4502,17 +4478,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1229474688</t>
+          <t>1386191168</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229474688</t>
+          <t>https://m.place.naver.com/place/1386191168</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4524,29 +4500,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>수피부과의원 파주운정점</t>
+          <t>알피부과의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>pajusooskin@naver.com</t>
+          <t>yeji0624@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1449-0506</t>
+          <t>031-911-7726</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 파주시 미래로 371 씨티타워 3층</t>
+          <t>경기도 고양시 일산서구 일현로 42</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sooskin2014/?next=%2F</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4556,7 +4532,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4577,17 +4553,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1492</v>
+        <v>240</v>
       </c>
       <c r="Q44" t="n">
-        <v>1532</v>
+        <v>7</v>
       </c>
       <c r="R44" t="n">
-        <v>3024</v>
+        <v>247</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4596,17 +4572,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>35003670</t>
+          <t>19534347</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35003670</t>
+          <t>https://m.place.naver.com/place/19534347</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4618,29 +4594,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>일산비타민의원</t>
+          <t>에스리영클리닉의원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jinjuvitaminclinic@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1406-2040</t>
+          <t>031-911-9313</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1426 일송노브레스</t>
+          <t>경기도 고양시 일산서구 중앙로 1426</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://www.vitaminskin.kr/</t>
+          <t>http://ilsanreyoung.co.kr/index.php</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4675,13 +4651,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>537</v>
+        <v>1</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4690,17 +4666,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>12776782</t>
+          <t>37383028</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12776782</t>
+          <t>https://m.place.naver.com/place/37383028</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4712,29 +4688,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>메이퓨어의원 일산점</t>
+          <t>리치성형외과의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jh9003__@naver.com</t>
+          <t>myidok@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>031-923-3196</t>
+          <t>0507-1472-3228</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 3층 301호</t>
+          <t>경기도 고양시 일산동구 정발산로 31-21 5층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>https://www.richprs.com/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4760,22 +4736,22 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>816</v>
+        <v>864</v>
       </c>
       <c r="Q46" t="n">
-        <v>459</v>
+        <v>52</v>
       </c>
       <c r="R46" t="n">
-        <v>1275</v>
+        <v>916</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4784,17 +4760,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1598670753</t>
+          <t>751902686</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598670753</t>
+          <t>https://m.place.naver.com/place/751902686</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4806,34 +4782,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>레이퀸의원</t>
+          <t>뷰티온의원 파주운정점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>islaqueen@naver.com</t>
+          <t>ejiee791105@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1448-1256</t>
+          <t>0507-1375-8428</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 219호</t>
+          <t>경기도 파주시 경의로 1068 7층 702호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/islaqueen</t>
+          <t>https://paju.beautyon.co.kr/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4843,7 +4819,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4854,22 +4830,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>149</v>
+        <v>1073</v>
       </c>
       <c r="Q47" t="n">
-        <v>936</v>
+        <v>1922</v>
       </c>
       <c r="R47" t="n">
-        <v>1085</v>
+        <v>2995</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4878,17 +4854,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1117977850</t>
+          <t>1997387146</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117977850</t>
+          <t>https://m.place.naver.com/place/1997387146</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4900,34 +4876,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>델타피부과의원</t>
+          <t>한사랑피부과의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tpdml02@naver.com</t>
+          <t>smtg5755@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1339-7565</t>
+          <t>031-918-3290</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 현대센트럴스퀘어 620호</t>
+          <t>경기도 고양시 일산서구 중앙로 1416 한사랑빌딩</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://deltaclinic.co.kr</t>
+          <t>http://www.pibucenter.co.kr/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4957,13 +4933,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="Q48" t="n">
-        <v>325</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>737</v>
+        <v>369</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4972,17 +4948,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1260275940</t>
+          <t>12971476</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260275940</t>
+          <t>https://m.place.naver.com/place/12971476</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4994,29 +4970,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>리치성형외과의원</t>
+          <t>연세영의원</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>myidok@naver.com</t>
+          <t>iqe02603@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1472-3228</t>
+          <t>031-947-2567</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-21 5층</t>
+          <t>경기도 파주시 경의로 1080 명동프라자 3층 307호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.richprs.com/</t>
+          <t>https://ys0clinic.co.kr/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5042,22 +5018,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>861</v>
+        <v>1541</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>627</v>
       </c>
       <c r="R49" t="n">
-        <v>913</v>
+        <v>2168</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5066,17 +5042,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>751902686</t>
+          <t>1538515183</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/751902686</t>
+          <t>https://m.place.naver.com/place/1538515183</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5088,39 +5064,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>메이에버의원</t>
+          <t>VS라인의원 일산점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2000kih@naver.com</t>
+          <t>vsline_official@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>031-983-6758</t>
+          <t>0507-1498-7031</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 250 골든타임 5층 메이에버의원</t>
+          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 3층 301호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://mayever.co.kr/</t>
+          <t>http://is.vsline.kr/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5136,22 +5112,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>262</v>
+        <v>1760</v>
       </c>
       <c r="Q50" t="n">
-        <v>34</v>
+        <v>8303</v>
       </c>
       <c r="R50" t="n">
-        <v>296</v>
+        <v>10063</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5160,17 +5136,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1027733049</t>
+          <t>1245507452</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027733049</t>
+          <t>https://m.place.naver.com/place/1245507452</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5182,29 +5158,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>벨피부과의원</t>
+          <t>스타필의원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>honma2005@naver.com</t>
+          <t>miandmo@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>031-902-4320</t>
+          <t>031-965-2255</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 경의로 315 설촌상가</t>
+          <t>경기도 고양시 덕양구 호국로789번길 6 중앙빌딩 3층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/miandmo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5214,12 +5190,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5239,13 +5215,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>320</v>
+        <v>273</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5254,17 +5230,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>13236957</t>
+          <t>20367149</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13236957</t>
+          <t>https://m.place.naver.com/place/20367149</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5276,34 +5252,38 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>예쁨톡톡의원</t>
+          <t>유앤아이의원 일산점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>seasons0907@naver.com</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>chiritachi197244@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mdvision@nate.com</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>031-943-5422</t>
+          <t>031-994-6021</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 파주시 초롱꽃로 109 4층 407호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 38-5 이레21빌딩 4층 401, 402, 403호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.isuni114.co.kr/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5324,22 +5304,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>213</v>
+        <v>802</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>4960</v>
       </c>
       <c r="R52" t="n">
-        <v>214</v>
+        <v>5762</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5348,17 +5328,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1919348740</t>
+          <t>1143822491</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919348740</t>
+          <t>https://m.place.naver.com/place/1143822491</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5370,29 +5350,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>데일리즈의원 일산</t>
+          <t>스노우의원 일산점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ldsmhan@naver.com</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>wkdwlxor30811@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>snowallrich@gmail.com</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>031-907-5400</t>
+          <t>0507-1436-1011</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 일산라페스타 E동 5층</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 61 6층 603~605-1호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://dailys.co.kr</t>
+          <t>https://ilsan-snow.co.kr/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5402,7 +5386,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5427,13 +5411,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>243</v>
+        <v>916</v>
       </c>
       <c r="Q53" t="n">
-        <v>1373</v>
+        <v>874</v>
       </c>
       <c r="R53" t="n">
-        <v>1616</v>
+        <v>1790</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5442,17 +5426,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13432168</t>
+          <t>1168348344</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13432168</t>
+          <t>https://m.place.naver.com/place/1168348344</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5464,29 +5448,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>닥터에버스의원 일산</t>
+          <t>365다움의원 파주운정</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>lavender_koko@naver.com</t>
+          <t>dawoomcl_paju@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1431-2093</t>
+          <t>0507-1350-5617</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티빌딩 3층</t>
+          <t>경기도 파주시 숲속노을로 128 서래메디컬프라자 4층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://evers5.co.kr</t>
+          <t>http://pf.kakao.com/_DxhEDn/chat</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5496,12 +5480,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5517,17 +5501,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>889</v>
+        <v>260</v>
       </c>
       <c r="Q54" t="n">
-        <v>2366</v>
+        <v>149</v>
       </c>
       <c r="R54" t="n">
-        <v>3255</v>
+        <v>409</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5536,17 +5520,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1023579945</t>
+          <t>2089239224</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023579945</t>
+          <t>https://m.place.naver.com/place/2089239224</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5558,29 +5542,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>365다움의원 파주운정</t>
+          <t>스노우의원 파주운정점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>dawoomcl_paju@naver.com</t>
+          <t>allbaro@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1350-5617</t>
+          <t>0507-1410-0913</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 파주시 숲속노을로 128 서래메디컬프라자 4층</t>
+          <t>경기도 파주시 경의로 1246 유은타워8차 2층 201호~205호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DxhEDn/chat</t>
+          <t>http://paju-snow.co.kr/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5590,12 +5574,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5611,17 +5595,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>256</v>
+        <v>1358</v>
       </c>
       <c r="Q55" t="n">
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="R55" t="n">
-        <v>394</v>
+        <v>1711</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5630,17 +5614,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2089239224</t>
+          <t>1338314528</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089239224</t>
+          <t>https://m.place.naver.com/place/1338314528</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5652,33 +5636,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>클린업피부과의원 일산</t>
+          <t>내안에봄의원 일산</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>cleanup-is@naver.com</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>promotion@cunetwork.co.kr</t>
-        </is>
-      </c>
+          <t>naeanebom@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1402-1877</t>
+          <t>0507-1391-8576</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1420 진영빌딩 5층</t>
+          <t>경기도 고양시 일산동구 강송로 33 벨라시타 쇼핑몰 1층 1102호 내안에봄의원 일산</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.upskin.co.kr/index_is.php?introClass=3&amp;introBranch=0</t>
+          <t>https://youtube.com/@pibuunnie</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5704,7 +5684,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5713,13 +5693,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1029</v>
+        <v>651</v>
       </c>
       <c r="Q56" t="n">
-        <v>693</v>
+        <v>1481</v>
       </c>
       <c r="R56" t="n">
-        <v>1722</v>
+        <v>2132</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5728,17 +5708,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>11874651</t>
+          <t>13584814</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11874651</t>
+          <t>https://m.place.naver.com/place/13584814</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5750,34 +5730,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>뷰티온의원 파주운정점</t>
+          <t>일산이지함피부과의원</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ejiee791105@naver.com</t>
+          <t>argecjd6260@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1375-8428</t>
+          <t>0507-1490-5301</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1068 7층 702호</t>
+          <t>경기도 고양시 일산서구 중앙로 1413 4층 이지함피부과</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://paju.beautyon.co.kr/</t>
+          <t>https://blog.naver.com/argecjd6260</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5787,7 +5767,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5798,22 +5778,22 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1066</v>
+        <v>428</v>
       </c>
       <c r="Q57" t="n">
-        <v>1815</v>
+        <v>52</v>
       </c>
       <c r="R57" t="n">
-        <v>2881</v>
+        <v>480</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5822,17 +5802,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1997387146</t>
+          <t>20038099</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997387146</t>
+          <t>https://m.place.naver.com/place/20038099</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5844,29 +5824,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>엘로디의원 파주운정본점</t>
+          <t>오킴스피부과의원</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>elodieclinic@naver.com</t>
+          <t>ohkims123456@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1372-8712</t>
+          <t>0507-1481-9335</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1204 월드타워10 4층 405호~410호</t>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창빌딩 10층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elodieclinic</t>
+          <t>https://www.ohkimsskin.com/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5892,22 +5872,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1037</v>
+        <v>915</v>
       </c>
       <c r="Q58" t="n">
-        <v>2086</v>
+        <v>41</v>
       </c>
       <c r="R58" t="n">
-        <v>3123</v>
+        <v>956</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5916,17 +5896,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1637191468</t>
+          <t>12776434</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637191468</t>
+          <t>https://m.place.naver.com/place/12776434</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5938,29 +5918,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>원피부과의원</t>
+          <t>수피부과의원 파주운정점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>beanb1n@naver.com</t>
+          <t>pajusooskin@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>031-904-0319</t>
+          <t>0507-1449-0506</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 179 신일산크리닉 401호</t>
+          <t>경기도 파주시 미래로 371 씨티타워 3층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sooskin2014/?next=%2F</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5970,7 +5950,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5991,17 +5971,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>378</v>
+        <v>1492</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>1630</v>
       </c>
       <c r="R59" t="n">
-        <v>386</v>
+        <v>3122</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6010,17 +5990,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11867907</t>
+          <t>35003670</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11867907</t>
+          <t>https://m.place.naver.com/place/35003670</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6032,33 +6012,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>스노우의원 일산점</t>
+          <t>메이린의원 일산</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wkdwlxor30811@naver.com</t>
+          <t>alawpearson@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>snowallrich@gmail.com</t>
+          <t>mkt@maylin.co.kr</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1436-1011</t>
+          <t>0507-1393-0000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 61 6층 603~605-1호</t>
+          <t>경기도 고양시 일산서구 호수로 817 현대백화점 킨텍스점 9층 메이린클리닉</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://ilsan-snow.co.kr/</t>
+          <t>https://www.maylin.co.kr/ilsan/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6093,13 +6073,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>904</v>
+        <v>69</v>
       </c>
       <c r="Q60" t="n">
-        <v>859</v>
+        <v>342</v>
       </c>
       <c r="R60" t="n">
-        <v>1763</v>
+        <v>411</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6108,17 +6088,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1168348344</t>
+          <t>19534963</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168348344</t>
+          <t>https://m.place.naver.com/place/19534963</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6130,29 +6110,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>일산이지함피부과의원</t>
+          <t>벨피부과의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>argecjd6260@naver.com</t>
+          <t>honma2005@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1490-5301</t>
+          <t>031-902-4320</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1413 4층 이지함피부과</t>
+          <t>경기도 고양시 일산동구 경의로 315 설촌상가</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/argecjd6260</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6162,12 +6142,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6187,13 +6167,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>428</v>
+        <v>320</v>
       </c>
       <c r="Q61" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="R61" t="n">
-        <v>480</v>
+        <v>326</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6202,17 +6182,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>20038099</t>
+          <t>13236957</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20038099</t>
+          <t>https://m.place.naver.com/place/13236957</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6224,29 +6204,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>예안의원</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>parknohsang@naver.com</t>
-        </is>
-      </c>
+          <t>최병문피부과의원</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>031-977-7579</t>
+          <t>031-965-5800</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 씨티프라자</t>
+          <t>경기도 고양시 덕양구 호국로 787 원당메디컬프라자</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://www.yeanclinic.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6256,7 +6232,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6281,13 +6257,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>492</v>
+        <v>977</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="R62" t="n">
-        <v>498</v>
+        <v>995</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6296,17 +6272,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>12063319</t>
+          <t>13237675</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12063319</t>
+          <t>https://m.place.naver.com/place/13237675</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6318,29 +6294,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>주엽 제일의원</t>
+          <t>클린업피부과의원 일산</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ske703@naver.com</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>cleanup-is@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>promotion@cunetwork.co.kr</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>031-918-8118</t>
+          <t>0507-1402-1877</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1437 화성프라자</t>
+          <t>경기도 고양시 일산서구 중앙로 1420 진영빌딩 5층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.upskin.co.kr/index_is.php?introClass=3&amp;introBranch=0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6350,12 +6330,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6371,17 +6351,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>173</v>
+        <v>1023</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="R63" t="n">
-        <v>173</v>
+        <v>1718</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6390,17 +6370,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>13237231</t>
+          <t>11874651</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237231</t>
+          <t>https://m.place.naver.com/place/11874651</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6412,34 +6392,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>미소가인피부과의원 일산점</t>
+          <t>예안의원</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>misogainep@naver.com</t>
+          <t>parknohsang@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>031-901-7603</t>
+          <t>031-977-7579</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 3층</t>
+          <t>경기도 고양시 일산서구 원일로 69 씨티프라자</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.misogain.co.kr/is/</t>
+          <t>http://www.yeanclinic.com/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6449,7 +6429,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6469,13 +6449,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>201</v>
+        <v>492</v>
       </c>
       <c r="Q64" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R64" t="n">
-        <v>212</v>
+        <v>498</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6484,17 +6464,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>13139640</t>
+          <t>12063319</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13139640</t>
+          <t>https://m.place.naver.com/place/12063319</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6506,34 +6486,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>연세영의원</t>
+          <t>온봄의원</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>iqe02603@naver.com</t>
+          <t>onbom_clinic@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>031-947-2567</t>
+          <t>0507-1323-0075</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1080 명동프라자 3층 307호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 45 C동 2층 218호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ys0clinic/</t>
+          <t>http://www.onbomclinic.co.kr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6563,13 +6543,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1534</v>
+        <v>249</v>
       </c>
       <c r="Q65" t="n">
-        <v>348</v>
+        <v>29</v>
       </c>
       <c r="R65" t="n">
-        <v>1882</v>
+        <v>278</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6578,17 +6558,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1538515183</t>
+          <t>1303562689</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538515183</t>
+          <t>https://m.place.naver.com/place/1303562689</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6600,29 +6580,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>에스리영클리닉의원</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>value_trend_guide@naver.com</t>
-        </is>
-      </c>
+          <t>베스트미의원</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>031-911-9313</t>
+          <t>031-907-3375</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1426</t>
+          <t>경기도 고양시 일산동구 일산로 229 글로리코아 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://ilsanreyoung.co.kr/index.php</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6632,7 +6608,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6657,13 +6633,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="R66" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6672,17 +6648,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>37383028</t>
+          <t>1084521027</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37383028</t>
+          <t>https://m.place.naver.com/place/1084521027</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6694,29 +6670,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>옐로우의원</t>
+          <t>포레의원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>heesunvly0826@naver.com</t>
+          <t>foreverilsan1@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>031-907-6111</t>
+          <t>0507-1309-8352</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 5층</t>
+          <t>경기도 고양시 일산동구 정발산로 38 401~402호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://www.yellowclinic.com</t>
+          <t>https://ilsanfore.co.kr</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6726,12 +6702,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6742,7 +6718,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6751,13 +6727,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="Q67" t="n">
-        <v>707</v>
+        <v>49</v>
       </c>
       <c r="R67" t="n">
-        <v>925</v>
+        <v>325</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6766,17 +6742,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>32047077</t>
+          <t>1596281549</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32047077</t>
+          <t>https://m.place.naver.com/place/1596281549</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6788,29 +6764,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>리버스의원 일산</t>
+          <t>미앤미의원 일산</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>dbsvlfwns1@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>abte1954@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>webtick@gmail.com</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1429-5556</t>
+          <t>0507-1411-8941</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 23 호수빌딩 502호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 8층 미앤미의원 일산</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://is.reverseclinic.com</t>
+          <t>http://is.mipretty.co.kr/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6820,7 +6800,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6845,13 +6825,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>750</v>
+        <v>592</v>
       </c>
       <c r="Q68" t="n">
-        <v>2557</v>
+        <v>3399</v>
       </c>
       <c r="R68" t="n">
-        <v>3307</v>
+        <v>3991</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6860,17 +6840,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>34508126</t>
+          <t>35135661</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34508126</t>
+          <t>https://m.place.naver.com/place/35135661</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6882,29 +6862,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>알피부과의원</t>
+          <t>메이에버의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yeji0624@naver.com</t>
+          <t>2000kih@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>031-911-7726</t>
+          <t>031-983-6758</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 42</t>
+          <t>경기도 김포시 김포한강1로 250 골든타임 5층 메이에버의원</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://mayever.co.kr/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6914,7 +6894,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6939,13 +6919,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="R69" t="n">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6954,17 +6934,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>19534347</t>
+          <t>1027733049</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19534347</t>
+          <t>https://m.place.naver.com/place/1027733049</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6976,34 +6956,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한사랑피부과의원</t>
+          <t>메이퓨어의원 일산점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>smtg5755@naver.com</t>
+          <t>jh9003__@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>031-918-3290</t>
+          <t>031-923-3196</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1416 한사랑빌딩</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 3층 301호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://www.pibucenter.co.kr/</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7024,22 +7004,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>362</v>
+        <v>830</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>457</v>
       </c>
       <c r="R70" t="n">
-        <v>369</v>
+        <v>1287</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7048,17 +7028,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>12971476</t>
+          <t>1598670753</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12971476</t>
+          <t>https://m.place.naver.com/place/1598670753</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7070,29 +7050,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>산타클로스의원 일산점</t>
+          <t>델타피부과의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sjwgroup0827@naver.com</t>
+          <t>tpdml02@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>031-905-7591</t>
+          <t>0507-1339-7565</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 55 산타클로스의원</t>
+          <t>경기도 김포시 김포한강1로 230 현대센트럴스퀘어 620호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://www.santaskin.co.kr/</t>
+          <t>https://deltaclinic.co.kr</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7118,7 +7098,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7127,13 +7107,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>272</v>
+        <v>414</v>
       </c>
       <c r="Q71" t="n">
-        <v>483</v>
+        <v>325</v>
       </c>
       <c r="R71" t="n">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7142,17 +7122,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13315650</t>
+          <t>1260275940</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13315650</t>
+          <t>https://m.place.naver.com/place/1260275940</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7221,13 +7201,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q72" t="n">
         <v>33</v>
       </c>
       <c r="R72" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7246,7 +7226,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7258,29 +7238,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>서울하나로의원</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ipkisdoctor@naver.com</t>
-        </is>
-      </c>
+          <t>성보의원</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1566-1706</t>
+          <t>031-966-7535</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1090 5층 504호~506호</t>
+          <t>경기도 고양시 덕양구 원당로125번길 12 원릉빌딩 201호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ipkisdoctor</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7290,12 +7266,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7315,13 +7291,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>537</v>
+        <v>428</v>
       </c>
       <c r="Q73" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>917</v>
+        <v>428</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7330,17 +7306,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>19517846</t>
+          <t>32614020</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19517846</t>
+          <t>https://m.place.naver.com/place/32614020</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7352,29 +7328,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>성보의원</t>
+          <t>서울하나로의원</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gokory@naver.com</t>
+          <t>ipkisdoctor@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>031-966-7535</t>
+          <t>1566-1706</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 원당로125번길 12 원릉빌딩 201호</t>
+          <t>경기도 파주시 경의로 1090 5층 504호~506호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ipkisdoctor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7384,12 +7360,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7409,13 +7385,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>428</v>
+        <v>537</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="R74" t="n">
-        <v>428</v>
+        <v>917</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7424,17 +7400,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>32614020</t>
+          <t>19517846</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32614020</t>
+          <t>https://m.place.naver.com/place/19517846</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7449,11 +7425,7 @@
           <t>장항중앙의원</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>dd0096@naver.com</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
@@ -7528,7 +7500,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7597,13 +7569,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="Q76" t="n">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="R76" t="n">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7622,7 +7594,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_derma/일산_피부과.xlsx
+++ b/naver-place-crawler/results_derma/일산_피부과.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>예쁨톡톡의원</t>
+          <t>닥터에버스의원 일산</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>seasons0907@naver.com</t>
+          <t>lavender_koko@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-943-5422</t>
+          <t>0507-1431-2093</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 파주시 초롱꽃로 109 4층 407호</t>
+          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티빌딩 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://evers5.co.kr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>218</v>
+        <v>890</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2385</v>
       </c>
       <c r="R2" t="n">
-        <v>219</v>
+        <v>3275</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1919348740</t>
+          <t>1023579945</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919348740</t>
+          <t>https://m.place.naver.com/place/1023579945</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더히엘의원</t>
+          <t>미소가인피부과의원 일산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thehielclinic@naver.com</t>
+          <t>misogainep@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1490-7910</t>
+          <t>031-901-7603</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 34 3층</t>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thehielclinic</t>
+          <t>http://www.misogain.co.kr/is/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>275</v>
+        <v>201</v>
       </c>
       <c r="Q3" t="n">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>435</v>
+        <v>212</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1282180214</t>
+          <t>13139640</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282180214</t>
+          <t>https://m.place.naver.com/place/13139640</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뷰티안의원</t>
+          <t>제너리스의원 일산</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>objms@naver.com</t>
+          <t>sgygag98@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1396-2816</t>
+          <t>031-904-9555</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타D 221호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/objms</t>
+          <t>https://is.generless.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>1491</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>7409</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>8900</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1398931993</t>
+          <t>1266922390</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1398931993</t>
+          <t>https://m.place.naver.com/place/1266922390</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미소가인피부과의원 일산점</t>
+          <t>위시티아름다운의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>misogainep@naver.com</t>
+          <t>wicitybeauty@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-901-7603</t>
+          <t>031-962-5350</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 3층</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워 3층 302호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.misogain.co.kr/is/</t>
+          <t>https://blog.naver.com/wicitybeauty</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13139640</t>
+          <t>1707720691</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13139640</t>
+          <t>https://m.place.naver.com/place/1707720691</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>사적인 아름다움 지유의원 일산점</t>
+          <t>한사랑피부과의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rkawjs1891@naver.com</t>
+          <t>smtg5755@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>031-812-0196</t>
+          <t>031-918-3290</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 21 501호</t>
+          <t>경기도 고양시 일산서구 중앙로 1416 한사랑빌딩</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://ilsan.gu.clinic/kr</t>
+          <t>http://www.pibucenter.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3359</v>
+        <v>362</v>
       </c>
       <c r="Q6" t="n">
-        <v>3037</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>6396</v>
+        <v>369</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1686302028</t>
+          <t>12971476</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1686302028</t>
+          <t>https://m.place.naver.com/place/12971476</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>옐로우의원</t>
+          <t>클린업피부과의원 일산</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>heesunvly0826@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>cleanup-is@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>promotion@cunetwork.co.kr</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-907-6111</t>
+          <t>0507-1402-1877</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 5층</t>
+          <t>경기도 고양시 일산서구 중앙로 1420 진영빌딩 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.yellowclinic.com</t>
+          <t>https://www.upskin.co.kr/index_is.php?introClass=3&amp;introBranch=0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,17 +1091,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>217</v>
+        <v>1023</v>
       </c>
       <c r="Q7" t="n">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="R7" t="n">
-        <v>924</v>
+        <v>1718</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>32047077</t>
+          <t>11874651</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32047077</t>
+          <t>https://m.place.naver.com/place/11874651</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>일산의원</t>
+          <t>내안에봄의원 일산</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medi114_official@naver.com</t>
+          <t>naeanebom@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-976-1240</t>
+          <t>0507-1391-8576</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 691</t>
+          <t>경기도 고양시 일산동구 강송로 33 벨라시타 쇼핑몰 1층 1102호 내안에봄의원 일산</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@pibuunnie</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,12 +1164,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1180,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>205</v>
+        <v>652</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1479</v>
       </c>
       <c r="R8" t="n">
-        <v>207</v>
+        <v>2131</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13237890</t>
+          <t>13584814</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237890</t>
+          <t>https://m.place.naver.com/place/13584814</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1222,44 +1226,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>위시티아름다운의원</t>
+          <t>앤유의원</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wicitybeauty@naver.com</t>
+          <t>relized71026@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-962-5350</t>
+          <t>0507-1359-2994</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워 3층 302호</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 55 효산캐슬빌딩 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wicitybeauty</t>
+          <t>http://nuclinic.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1270,22 +1274,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="R9" t="n">
-        <v>195</v>
+        <v>558</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1707720691</t>
+          <t>1109875670</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707720691</t>
+          <t>https://m.place.naver.com/place/1109875670</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1316,39 +1320,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스무살의원</t>
+          <t>메이린의원 일산</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>drkwun@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>alawpearson@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mkt@maylin.co.kr</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-932-9737</t>
+          <t>0507-1393-0000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔1</t>
+          <t>경기도 고양시 일산서구 호수로 817 현대백화점 킨텍스점 9층 메이린클리닉</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://smoothall.com/</t>
+          <t>https://www.maylin.co.kr/ilsan/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1373,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>691</v>
+        <v>71</v>
       </c>
       <c r="Q10" t="n">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="R10" t="n">
-        <v>972</v>
+        <v>413</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>31310223</t>
+          <t>19534963</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31310223</t>
+          <t>https://m.place.naver.com/place/19534963</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1410,39 +1418,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리뉴앤영의원</t>
+          <t>레이퀸의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>twitchy378386@naver.com</t>
+          <t>islaqueen@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1355-2651</t>
+          <t>0507-1448-1256</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-9 레이크프라자2, 5층</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 219호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.renew-young.com/</t>
+          <t>https://blog.naver.com/islaqueen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1458,22 +1466,22 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>887</v>
+        <v>149</v>
       </c>
       <c r="Q11" t="n">
-        <v>217</v>
+        <v>948</v>
       </c>
       <c r="R11" t="n">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1463393218</t>
+          <t>1117977850</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463393218</t>
+          <t>https://m.place.naver.com/place/1117977850</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1504,39 +1512,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레이퀸의원</t>
+          <t>스노우의원 일산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>islaqueen@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>wkdwlxor30811@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>snowallrich@gmail.com</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1448-1256</t>
+          <t>0507-1436-1011</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 219호</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 61 6층 603~605-1호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/islaqueen</t>
+          <t>https://ilsan-snow.co.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1552,22 +1564,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>149</v>
+        <v>923</v>
       </c>
       <c r="Q12" t="n">
-        <v>943</v>
+        <v>881</v>
       </c>
       <c r="R12" t="n">
-        <v>1092</v>
+        <v>1804</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1588,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1117977850</t>
+          <t>1168348344</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117977850</t>
+          <t>https://m.place.naver.com/place/1168348344</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1598,34 +1610,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>데일리즈의원 일산</t>
+          <t>엘로디의원 파주운정본점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ldsmhan@naver.com</t>
+          <t>elodieclinic@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>031-907-5400</t>
+          <t>0507-1372-8712</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 일산라페스타 E동 5층</t>
+          <t>경기도 파주시 경의로 1204 월드타워10 4층 405호~410호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://dailys.co.kr</t>
+          <t>https://blog.naver.com/elodieclinic</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1646,7 +1658,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1667,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>245</v>
+        <v>1059</v>
       </c>
       <c r="Q13" t="n">
-        <v>1456</v>
+        <v>1610</v>
       </c>
       <c r="R13" t="n">
-        <v>1701</v>
+        <v>2669</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1682,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13432168</t>
+          <t>1637191468</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13432168</t>
+          <t>https://m.place.naver.com/place/1637191468</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1704,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>스카이비뇨의학과의원</t>
+          <t>예안의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>skyuroskin@naver.com</t>
+          <t>parknohsang@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>031-813-7582</t>
+          <t>031-977-7579</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을1로 73 신성메디칼타운 601호</t>
+          <t>경기도 고양시 일산서구 원일로 69 씨티프라자</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skyuroskin</t>
+          <t>http://www.yeanclinic.com/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1729,7 +1741,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1749,13 +1761,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>412</v>
+        <v>492</v>
       </c>
       <c r="Q14" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>443</v>
+        <v>498</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1776,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1050410147</t>
+          <t>12063319</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050410147</t>
+          <t>https://m.place.naver.com/place/12063319</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1786,40 +1798,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일산비타민의원</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>톤즈의원 일산</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dpilsan@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1406-2040</t>
+          <t>0507-1329-1753</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1426 일송노브레스</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 61 4층 톤즈의원 일산</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://www.vitaminskin.kr/</t>
+          <t>https://tonesclinic.co.kr/ilsan</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1830,22 +1846,22 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>529</v>
+        <v>4324</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>5675</v>
       </c>
       <c r="R15" t="n">
-        <v>535</v>
+        <v>9999</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1870,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>12776782</t>
+          <t>1053186040</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12776782</t>
+          <t>https://m.place.naver.com/place/1053186040</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1876,30 +1892,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>주엽 제일의원</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>하얀나라피부과의원</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>guswjd9408@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>031-918-8118</t>
+          <t>031-972-4333</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1437 화성프라자</t>
+          <t>경기도 고양시 덕양구 화중로 76 5층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.white365.co.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1929,13 +1949,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>173</v>
+        <v>656</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>173</v>
+        <v>661</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1964,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13237231</t>
+          <t>13237811</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237231</t>
+          <t>https://m.place.naver.com/place/13237811</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1986,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>닥터에버스의원 일산</t>
+          <t>온봄의원</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lavender_koko@naver.com</t>
+          <t>onbom_clinic@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1431-2093</t>
+          <t>0507-1323-0075</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티빌딩 3층</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 45 C동 2층 218호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://evers5.co.kr</t>
+          <t>http://www.onbomclinic.co.kr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1998,12 +2018,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2014,7 +2034,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2023,13 +2043,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>889</v>
+        <v>249</v>
       </c>
       <c r="Q17" t="n">
-        <v>2381</v>
+        <v>29</v>
       </c>
       <c r="R17" t="n">
-        <v>3270</v>
+        <v>278</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2058,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1023579945</t>
+          <t>1303562689</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023579945</t>
+          <t>https://m.place.naver.com/place/1303562689</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2060,34 +2080,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>산타클로스의원 일산점</t>
+          <t>일산비타민의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sjwgroup0827@naver.com</t>
+          <t>jinjuvitaminclinic@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>031-905-7591</t>
+          <t>0507-1406-2040</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 55 산타클로스의원</t>
+          <t>경기도 고양시 일산서구 중앙로 1426 일송노브레스</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://www.santaskin.co.kr/</t>
+          <t>http://www.vitaminskin.kr/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2108,7 +2128,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2137,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>272</v>
+        <v>528</v>
       </c>
       <c r="Q18" t="n">
-        <v>483</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>755</v>
+        <v>534</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2152,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13315650</t>
+          <t>12776782</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13315650</t>
+          <t>https://m.place.naver.com/place/12776782</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2174,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>고은미래의원 일산점</t>
+          <t>스무살의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>go9037600@naver.com</t>
+          <t>drkwun@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1380-7601</t>
+          <t>031-932-9737</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 22 진넥스블루오션 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/go9037600</t>
+          <t>http://smoothall.com/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2202,22 +2222,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>534</v>
+        <v>689</v>
       </c>
       <c r="Q19" t="n">
-        <v>204</v>
+        <v>285</v>
       </c>
       <c r="R19" t="n">
-        <v>738</v>
+        <v>974</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,17 +2246,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1770208123</t>
+          <t>31310223</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1770208123</t>
+          <t>https://m.place.naver.com/place/31310223</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2248,29 +2268,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>파크뷰의원 운정점</t>
+          <t>리치성형외과의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>thdwjdals25@naver.com</t>
+          <t>myidok@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>031-939-1100</t>
+          <t>0507-1472-3228</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 507 월드타워9차 6층</t>
+          <t>경기도 고양시 일산동구 정발산로 31-21 5층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pskin.kr/</t>
+          <t>https://www.richprs.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,7 +2305,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2296,22 +2316,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1139</v>
+        <v>861</v>
       </c>
       <c r="Q20" t="n">
-        <v>1959</v>
+        <v>52</v>
       </c>
       <c r="R20" t="n">
-        <v>3098</v>
+        <v>913</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,17 +2340,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>33021543</t>
+          <t>751902686</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33021543</t>
+          <t>https://m.place.naver.com/place/751902686</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2362,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>제너리스의원 일산</t>
+          <t>연세다안피부과의원</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sgygag98@naver.com</t>
+          <t>bluecoread@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>031-904-9555</t>
+          <t>031-994-3322</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 4층</t>
+          <t>경기도 고양시 덕양구 화정로 53-1 글로리아빌딩 205호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://is.generless.com</t>
+          <t>http://ysdaanderma.com</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2390,22 +2410,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1488</v>
+        <v>378</v>
       </c>
       <c r="Q21" t="n">
-        <v>7344</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>8832</v>
+        <v>381</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,17 +2434,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1266922390</t>
+          <t>1028421543</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266922390</t>
+          <t>https://m.place.naver.com/place/1028421543</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2436,29 +2456,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>유노라의원</t>
+          <t>VS라인의원 일산점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>vivaclinic@naver.com</t>
+          <t>vsline_official@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>031-923-7774</t>
+          <t>0507-1498-7031</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 GIFC 오피스동 4층 403호</t>
+          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 3층 301호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.eunoraclinic.com</t>
+          <t>http://is.vsline.kr/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2473,7 +2493,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2493,13 +2513,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>729</v>
+        <v>1777</v>
       </c>
       <c r="Q22" t="n">
-        <v>576</v>
+        <v>8691</v>
       </c>
       <c r="R22" t="n">
-        <v>1305</v>
+        <v>10468</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2508,17 +2528,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1267159783</t>
+          <t>1245507452</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267159783</t>
+          <t>https://m.place.naver.com/place/1245507452</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2530,29 +2550,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>리버스의원 일산</t>
+          <t>고은미래의원 일산점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dbsvlfwns1@naver.com</t>
+          <t>go9037600@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1429-5556</t>
+          <t>0507-1380-7601</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 23 호수빌딩 502호</t>
+          <t>경기도 고양시 일산동구 숲속마을로 22 진넥스블루오션 2층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://is.reverseclinic.com</t>
+          <t>https://blog.naver.com/go9037600</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2578,22 +2598,22 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>752</v>
+        <v>537</v>
       </c>
       <c r="Q23" t="n">
-        <v>2254</v>
+        <v>204</v>
       </c>
       <c r="R23" t="n">
-        <v>3006</v>
+        <v>741</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2622,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>34508126</t>
+          <t>1770208123</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34508126</t>
+          <t>https://m.place.naver.com/place/1770208123</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2644,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>일산고운세상피부과의원</t>
+          <t>에스리영클리닉의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gwssskin@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>031-932-8275</t>
+          <t>031-911-9313</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 웅신아트 4층</t>
+          <t>경기도 고양시 일산서구 중앙로 1426</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://www.gowoonss.com/ilsan</t>
+          <t>http://ilsanreyoung.co.kr/index.php</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2661,7 +2681,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2672,7 +2692,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2681,13 +2701,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>633</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1029</v>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2716,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13096274</t>
+          <t>37383028</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13096274</t>
+          <t>https://m.place.naver.com/place/37383028</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2718,25 +2738,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>블리비의원 일산점</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>최병문피부과의원</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cleanz77@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1833-7382</t>
+          <t>031-965-5800</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티 2층</t>
+          <t>경기도 고양시 덕양구 호국로 787 원당메디컬프라자</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.velyb.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2746,7 +2770,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2771,13 +2795,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>5990</v>
+        <v>977</v>
       </c>
       <c r="Q25" t="n">
-        <v>4685</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>10675</v>
+        <v>995</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2810,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1592961756</t>
+          <t>13237675</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1592961756</t>
+          <t>https://m.place.naver.com/place/13237675</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2808,39 +2832,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>톤즈의원 일산</t>
+          <t>일산이지함피부과의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dpilsan@naver.com</t>
+          <t>argecjd6260@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1329-1753</t>
+          <t>0507-1490-5301</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 61 4층 톤즈의원 일산</t>
+          <t>경기도 고양시 일산서구 중앙로 1413 4층 이지함피부과</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://tonesclinic.co.kr/ilsan</t>
+          <t>https://blog.naver.com/argecjd6260</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2856,22 +2880,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4292</v>
+        <v>428</v>
       </c>
       <c r="Q26" t="n">
-        <v>5509</v>
+        <v>53</v>
       </c>
       <c r="R26" t="n">
-        <v>9801</v>
+        <v>481</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2904,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1053186040</t>
+          <t>20038099</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053186040</t>
+          <t>https://m.place.naver.com/place/20038099</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2902,29 +2926,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>웰스피부과의원</t>
+          <t>옐로우의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>wellspaju123@naver.com</t>
+          <t>heesunvly0826@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-943-2374</t>
+          <t>031-907-6111</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 133 형성프라자 3층</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 5층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.wellsclinicpaju.co.kr/</t>
+          <t>http://www.yellowclinic.com</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2934,12 +2958,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2950,7 +2974,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2959,13 +2983,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>544</v>
+        <v>217</v>
       </c>
       <c r="Q27" t="n">
-        <v>174</v>
+        <v>707</v>
       </c>
       <c r="R27" t="n">
-        <v>718</v>
+        <v>924</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2998,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1941007069</t>
+          <t>32047077</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941007069</t>
+          <t>https://m.place.naver.com/place/32047077</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2996,29 +3020,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>봄날초이스의원</t>
+          <t>벨피부과의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bomnalp@naver.com</t>
+          <t>drpjl@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1418-0888</t>
+          <t>031-902-4320</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 후곡로 22 신일빌딩 2층</t>
+          <t>경기도 고양시 일산동구 경의로 315 설촌상가</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://bomnals.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3028,7 +3052,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3053,13 +3077,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>794</v>
+        <v>320</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>798</v>
+        <v>326</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3092,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11597476</t>
+          <t>13236957</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11597476</t>
+          <t>https://m.place.naver.com/place/13236957</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3090,34 +3114,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>밴스의원 일산</t>
+          <t>베스트미의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>vandsis@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>031-994-0380</t>
+          <t>031-907-3375</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 6층 601, 603호</t>
+          <t>경기도 고양시 일산동구 일산로 229 글로리코아 2층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://ilsan.vandsclinic.co.kr/?channel=1687</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3127,7 +3151,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3138,22 +3162,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1386</v>
+        <v>167</v>
       </c>
       <c r="Q29" t="n">
-        <v>3542</v>
+        <v>110</v>
       </c>
       <c r="R29" t="n">
-        <v>4928</v>
+        <v>277</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3186,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1481200696</t>
+          <t>1084521027</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481200696</t>
+          <t>https://m.place.naver.com/place/1084521027</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3184,34 +3208,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>유진피부과의원</t>
+          <t>하얀나라김피부과의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>d0ig-785m6a@naver.com</t>
+          <t>seain57@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>031-917-6749</t>
+          <t>031-917-7588</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강선로 59 동신파크빌딩</t>
+          <t>경기도 고양시 일산서구 일산로 576 대성프라자</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.laser2u.com/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3241,13 +3265,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>517</v>
+        <v>1303</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>523</v>
+        <v>1317</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3280,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>13237201</t>
+          <t>11535528</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237201</t>
+          <t>https://m.place.naver.com/place/11535528</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3278,34 +3302,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>메디누리미의원</t>
+          <t>아비쥬의원 일산</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>abijou0@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-915-7577</t>
+          <t>1544-0377</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 53</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 64 홈플러스 일산점 4층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.abijouclinicis.com</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3315,7 +3339,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3326,22 +3350,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>124</v>
+        <v>4778</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>2258</v>
       </c>
       <c r="R31" t="n">
-        <v>127</v>
+        <v>7036</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3374,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>35418720</t>
+          <t>1229474688</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35418720</t>
+          <t>https://m.place.naver.com/place/1229474688</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3372,29 +3396,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>일산차앤박피부과의원</t>
+          <t>산타클로스의원 일산점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ilsan_cnp@naver.com</t>
+          <t>sjwgroup0827@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>031-911-7571</t>
+          <t>031-905-7591</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1441 하나은행 건물 5층</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 55 산타클로스의원</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://ilsancnp.com/</t>
+          <t>http://www.santaskin.co.kr/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3429,13 +3453,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>386</v>
+        <v>272</v>
       </c>
       <c r="Q32" t="n">
-        <v>667</v>
+        <v>483</v>
       </c>
       <c r="R32" t="n">
-        <v>1053</v>
+        <v>755</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3468,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>32528322</t>
+          <t>13315650</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32528322</t>
+          <t>https://m.place.naver.com/place/13315650</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3466,34 +3490,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>원피부과의원</t>
+          <t>유노라의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>beanb1n@naver.com</t>
+          <t>vivaclinic@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>031-904-0319</t>
+          <t>031-923-7774</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 179 신일산크리닉 401호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 GIFC 오피스동 4층 403호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.eunoraclinic.com</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3503,7 +3527,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3514,22 +3538,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>379</v>
+        <v>729</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>574</v>
       </c>
       <c r="R33" t="n">
-        <v>387</v>
+        <v>1303</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3562,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11867907</t>
+          <t>1267159783</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11867907</t>
+          <t>https://m.place.naver.com/place/1267159783</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3560,29 +3584,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>하얀나라김피부과의원</t>
+          <t>365다움의원 파주운정역</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>imagine77-@naver.com</t>
+          <t>dawoomcl_paju@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>031-917-7588</t>
+          <t>0507-1350-5617</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 576 대성프라자</t>
+          <t>경기도 파주시 숲속노을로 128 서래메디컬프라자 4층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.laser2u.com/</t>
+          <t>http://pf.kakao.com/_DxhEDn/chat</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3592,7 +3616,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3608,7 +3632,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3617,13 +3641,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1303</v>
+        <v>260</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="R34" t="n">
-        <v>1317</v>
+        <v>415</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,17 +3656,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11535528</t>
+          <t>2089239224</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11535528</t>
+          <t>https://m.place.naver.com/place/2089239224</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3654,29 +3678,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>루미엘의원</t>
+          <t>일산차앤박피부과의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cliniclumiere@naver.com</t>
+          <t>ilsan_cnp@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1350-6971</t>
+          <t>031-911-7571</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로515번길 91 프라임타워 6층 607호</t>
+          <t>경기도 고양시 일산서구 중앙로 1441 하나은행 건물 5층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://cliniclumiere.com/</t>
+          <t>http://ilsancnp.com/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3691,7 +3715,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3711,13 +3735,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="Q35" t="n">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="R35" t="n">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,17 +3750,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1267511624</t>
+          <t>32528322</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267511624</t>
+          <t>https://m.place.naver.com/place/32528322</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3748,29 +3772,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>루체피부과의원</t>
+          <t>미앤미의원 일산</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>luceskin11@naver.com</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>abte1954@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>webtick@gmail.com</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>031-917-8088</t>
+          <t>0507-1411-8941</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1444 태원빌딩 4층</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 8층 미앤미의원 일산</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://www.luce-skin.com/</t>
+          <t>http://is.mipretty.co.kr/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3780,12 +3808,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3796,22 +3824,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>418</v>
+        <v>605</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>3456</v>
       </c>
       <c r="R36" t="n">
-        <v>442</v>
+        <v>4061</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,17 +3848,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11531592</t>
+          <t>35135661</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11531592</t>
+          <t>https://m.place.naver.com/place/35135661</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3842,44 +3870,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>더드림의원 일산</t>
+          <t>원피부과의원</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>micketionath53857@naver.com</t>
+          <t>beanb1n@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1307-7365</t>
+          <t>031-904-0319</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 4층</t>
+          <t>경기도 고양시 일산동구 강송로 179 신일산크리닉 401호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://thedreamskin.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3890,7 +3918,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3899,13 +3927,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>748</v>
+        <v>379</v>
       </c>
       <c r="Q37" t="n">
-        <v>437</v>
+        <v>8</v>
       </c>
       <c r="R37" t="n">
-        <v>1185</v>
+        <v>387</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,17 +3942,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1178991103</t>
+          <t>11867907</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178991103</t>
+          <t>https://m.place.naver.com/place/11867907</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3936,29 +3964,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>김영숙피부과의원</t>
+          <t>메이퓨어의원 일산점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dermakims@naver.com</t>
+          <t>jh9003__@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>031-901-3133</t>
+          <t>031-923-3196</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1124 이마트 2층 김영숙피부과</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 3층 301호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://www.skinkim.net/</t>
+          <t>https://www.maypureclinic.com/ko/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3968,12 +3996,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3984,22 +4012,22 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1960</v>
+        <v>835</v>
       </c>
       <c r="Q38" t="n">
-        <v>289</v>
+        <v>457</v>
       </c>
       <c r="R38" t="n">
-        <v>2249</v>
+        <v>1292</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4036,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>13236932</t>
+          <t>1598670753</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13236932</t>
+          <t>https://m.place.naver.com/place/1598670753</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4030,44 +4058,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>앤유의원</t>
+          <t>더히엘의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>relized71026@naver.com</t>
+          <t>thehielclinic@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1359-2994</t>
+          <t>0507-1490-7910</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 55 효산캐슬빌딩 4층</t>
+          <t>경기도 고양시 일산동구 위시티로 34 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://nuclinic.co.kr/</t>
+          <t>https://blog.naver.com/thehielclinic</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4078,7 +4106,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4087,13 +4115,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>157</v>
+        <v>275</v>
       </c>
       <c r="Q39" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="R39" t="n">
-        <v>557</v>
+        <v>435</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4130,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1109875670</t>
+          <t>1282180214</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109875670</t>
+          <t>https://m.place.naver.com/place/1282180214</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4124,34 +4152,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>다시봄날의원 파주점</t>
+          <t>오킴스피부과의원</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>springdayclinic22@naver.com</t>
+          <t>ohkims123456@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1468-7666</t>
+          <t>0507-1481-9335</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1074 삼융시네마 405호</t>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창빌딩 10층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://pj.springdayclinic.com/</t>
+          <t>https://www.ohkimsskin.com/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4177,17 +4205,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>872</v>
+        <v>915</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R40" t="n">
-        <v>882</v>
+        <v>958</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4224,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1800857823</t>
+          <t>12776434</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1800857823</t>
+          <t>https://m.place.naver.com/place/12776434</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4218,34 +4246,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>엘로디의원 파주운정본점</t>
+          <t>다시봄날의원 파주점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>elodieclinic@naver.com</t>
+          <t>springdayclinic22@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1372-8712</t>
+          <t>0507-1468-7666</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1204 월드타워10 4층 405호~410호</t>
+          <t>경기도 파주시 경의로 1074 삼융시네마 405호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elodieclinic</t>
+          <t>https://pj.springdayclinic.com/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4266,7 +4294,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4275,13 +4303,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1051</v>
+        <v>876</v>
       </c>
       <c r="Q41" t="n">
-        <v>1596</v>
+        <v>10</v>
       </c>
       <c r="R41" t="n">
-        <v>2647</v>
+        <v>886</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4318,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1637191468</t>
+          <t>1800857823</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637191468</t>
+          <t>https://m.place.naver.com/place/1800857823</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4312,44 +4340,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아비쥬의원 일산</t>
+          <t>루체피부과의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abijou0@naver.com</t>
+          <t>luceskin11@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1544-0377</t>
+          <t>031-917-8088</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 64 홈플러스 일산점 4층</t>
+          <t>경기도 고양시 일산서구 중앙로 1444 태원빌딩 4층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://www.abijouclinicis.com</t>
+          <t>http://www.luce-skin.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4360,22 +4388,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4774</v>
+        <v>418</v>
       </c>
       <c r="Q42" t="n">
-        <v>2140</v>
+        <v>24</v>
       </c>
       <c r="R42" t="n">
-        <v>6914</v>
+        <v>442</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4412,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1229474688</t>
+          <t>11531592</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229474688</t>
+          <t>https://m.place.naver.com/place/11531592</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4406,29 +4434,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>일산주엽 톡스앤필의원</t>
+          <t>블리비의원 일산점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ilsantox@naver.com</t>
+          <t>lukxymxl@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>031-994-0188</t>
+          <t>1833-7382</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1413 동영빌딩 3층</t>
+          <t>경기도 고양시 일산동구 정발산로 38 이스턴시티 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ilsantox</t>
+          <t>http://www.velyb.kr</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4443,7 +4471,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4459,17 +4487,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1186</v>
+        <v>6032</v>
       </c>
       <c r="Q43" t="n">
-        <v>2080</v>
+        <v>4736</v>
       </c>
       <c r="R43" t="n">
-        <v>3266</v>
+        <v>10768</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4478,17 +4506,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1386191168</t>
+          <t>1592961756</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386191168</t>
+          <t>https://m.place.naver.com/place/1592961756</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4500,29 +4528,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>알피부과의원</t>
+          <t>봄날초이스의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>yeji0624@naver.com</t>
+          <t>bomnalp@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>031-911-7726</t>
+          <t>0507-1418-0888</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 42</t>
+          <t>경기도 고양시 일산서구 후곡로 22 신일빌딩 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://bomnals.co.kr</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4532,7 +4560,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4557,13 +4585,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>240</v>
+        <v>794</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>247</v>
+        <v>798</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4572,17 +4600,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>19534347</t>
+          <t>11597476</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19534347</t>
+          <t>https://m.place.naver.com/place/11597476</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4594,29 +4622,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에스리영클리닉의원</t>
+          <t>메이에버의원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>2000kih@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>031-911-9313</t>
+          <t>031-983-6758</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1426</t>
+          <t>경기도 김포시 김포한강1로 250 골든타임 5층 메이에버의원</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://ilsanreyoung.co.kr/index.php</t>
+          <t>http://mayever.co.kr/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4651,13 +4679,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4666,17 +4694,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>37383028</t>
+          <t>1027733049</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37383028</t>
+          <t>https://m.place.naver.com/place/1027733049</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4688,34 +4716,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>리치성형외과의원</t>
+          <t>일산주엽 톡스앤필의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>myidok@naver.com</t>
+          <t>ilsantox@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1472-3228</t>
+          <t>031-994-0188</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-21 5층</t>
+          <t>경기도 고양시 일산서구 중앙로 1413 동영빌딩 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.richprs.com/</t>
+          <t>https://blog.naver.com/ilsantox</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4725,7 +4753,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4741,17 +4769,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>864</v>
+        <v>1203</v>
       </c>
       <c r="Q46" t="n">
-        <v>52</v>
+        <v>2112</v>
       </c>
       <c r="R46" t="n">
-        <v>916</v>
+        <v>3315</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4760,17 +4788,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>751902686</t>
+          <t>1386191168</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/751902686</t>
+          <t>https://m.place.naver.com/place/1386191168</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4782,29 +4810,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>뷰티온의원 파주운정점</t>
+          <t>델타피부과의원</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ejiee791105@naver.com</t>
+          <t>tpdml02@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1375-8428</t>
+          <t>0507-1339-7565</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1068 7층 702호</t>
+          <t>경기도 김포시 김포한강1로 230 현대센트럴스퀘어 620호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://paju.beautyon.co.kr/</t>
+          <t>https://deltaclinic.co.kr</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4830,22 +4858,22 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1073</v>
+        <v>413</v>
       </c>
       <c r="Q47" t="n">
-        <v>1922</v>
+        <v>325</v>
       </c>
       <c r="R47" t="n">
-        <v>2995</v>
+        <v>738</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4854,17 +4882,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1997387146</t>
+          <t>1260275940</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1997387146</t>
+          <t>https://m.place.naver.com/place/1260275940</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4876,44 +4904,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한사랑피부과의원</t>
+          <t>리뉴앤영의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>smtg5755@naver.com</t>
+          <t>twitchy378386@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>031-918-3290</t>
+          <t>0507-1355-2651</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1416 한사랑빌딩</t>
+          <t>경기도 고양시 일산동구 정발산로 31-9 레이크프라자2, 5층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://www.pibucenter.co.kr/</t>
+          <t>https://www.renew-young.com/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4924,22 +4952,22 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>362</v>
+        <v>888</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>219</v>
       </c>
       <c r="R48" t="n">
-        <v>369</v>
+        <v>1107</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4948,17 +4976,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>12971476</t>
+          <t>1463393218</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12971476</t>
+          <t>https://m.place.naver.com/place/1463393218</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4970,34 +4998,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>연세영의원</t>
+          <t>더드림의원 일산</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>iqe02603@naver.com</t>
+          <t>micketionath53857@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>031-947-2567</t>
+          <t>0507-1307-7365</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1080 명동프라자 3층 307호</t>
+          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 4층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://ys0clinic.co.kr/</t>
+          <t>https://blog.naver.com/micketionath53857</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5007,7 +5035,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5018,22 +5046,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1541</v>
+        <v>748</v>
       </c>
       <c r="Q49" t="n">
-        <v>627</v>
+        <v>437</v>
       </c>
       <c r="R49" t="n">
-        <v>2168</v>
+        <v>1185</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5042,17 +5070,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1538515183</t>
+          <t>1178991103</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538515183</t>
+          <t>https://m.place.naver.com/place/1178991103</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5064,29 +5092,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VS라인의원 일산점</t>
+          <t>데일리즈의원 일산</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>vsline_official@naver.com</t>
+          <t>ldsmhan@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1498-7031</t>
+          <t>031-907-5400</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-17 킹타운 3층 301호</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 일산라페스타 E동 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://is.vsline.kr/</t>
+          <t>http://dailys.co.kr</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5096,12 +5124,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5121,13 +5149,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1760</v>
+        <v>252</v>
       </c>
       <c r="Q50" t="n">
-        <v>8303</v>
+        <v>1496</v>
       </c>
       <c r="R50" t="n">
-        <v>10063</v>
+        <v>1748</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5136,17 +5164,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1245507452</t>
+          <t>13432168</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245507452</t>
+          <t>https://m.place.naver.com/place/13432168</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5158,39 +5186,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>스타필의원</t>
+          <t>김영숙피부과의원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>miandmo@naver.com</t>
+          <t>dermakims@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>031-965-2255</t>
+          <t>031-901-3133</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 호국로789번길 6 중앙빌딩 3층</t>
+          <t>경기도 고양시 일산동구 중앙로 1124 이마트 2층 김영숙피부과</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miandmo</t>
+          <t>http://www.skinkim.net/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5215,13 +5243,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>273</v>
+        <v>1961</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>289</v>
       </c>
       <c r="R51" t="n">
-        <v>277</v>
+        <v>2250</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5230,17 +5258,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>20367149</t>
+          <t>13236932</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20367149</t>
+          <t>https://m.place.naver.com/place/13236932</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5252,38 +5280,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>유앤아이의원 일산점</t>
+          <t>알피부과의원</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>chiritachi197244@naver.com</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>mdvision@nate.com</t>
-        </is>
-      </c>
+          <t>yeji0624@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>031-994-6021</t>
+          <t>031-911-7726</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 38-5 이레21빌딩 4층 401, 402, 403호</t>
+          <t>경기도 고양시 일산서구 일현로 42</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.isuni114.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5304,22 +5328,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>802</v>
+        <v>240</v>
       </c>
       <c r="Q52" t="n">
-        <v>4960</v>
+        <v>7</v>
       </c>
       <c r="R52" t="n">
-        <v>5762</v>
+        <v>247</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5328,17 +5352,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1143822491</t>
+          <t>19534347</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1143822491</t>
+          <t>https://m.place.naver.com/place/19534347</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5350,38 +5374,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>스노우의원 일산점</t>
+          <t>메디누리미의원</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wkdwlxor30811@naver.com</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>snowallrich@gmail.com</t>
-        </is>
-      </c>
+          <t>value_trend_guide@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1436-1011</t>
+          <t>031-915-7577</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 61 6층 603~605-1호</t>
+          <t>경기도 고양시 일산서구 일현로 53</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://ilsan-snow.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5391,7 +5411,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5402,22 +5422,22 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>916</v>
+        <v>126</v>
       </c>
       <c r="Q53" t="n">
-        <v>874</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>1790</v>
+        <v>129</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5426,17 +5446,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1168348344</t>
+          <t>35418720</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168348344</t>
+          <t>https://m.place.naver.com/place/35418720</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5448,29 +5468,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>365다움의원 파주운정</t>
+          <t>웰스피부과의원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>dawoomcl_paju@naver.com</t>
+          <t>wellspaju123@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1350-5617</t>
+          <t>031-943-2374</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 파주시 숲속노을로 128 서래메디컬프라자 4층</t>
+          <t>경기도 파주시 와석순환로 133 형성프라자 3층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DxhEDn/chat</t>
+          <t>https://www.wellsclinicpaju.co.kr/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5480,12 +5500,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5505,13 +5525,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>260</v>
+        <v>545</v>
       </c>
       <c r="Q54" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="R54" t="n">
-        <v>409</v>
+        <v>722</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5520,17 +5540,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2089239224</t>
+          <t>1941007069</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089239224</t>
+          <t>https://m.place.naver.com/place/1941007069</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5542,29 +5562,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>스노우의원 파주운정점</t>
+          <t>연세영의원</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>allbaro@naver.com</t>
+          <t>iqe02603@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1410-0913</t>
+          <t>031-947-2567</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1246 유은타워8차 2층 201호~205호</t>
+          <t>경기도 파주시 경의로 1080 명동프라자 3층 307호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://paju-snow.co.kr/</t>
+          <t>https://ys0clinic.co.kr/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5579,7 +5599,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5599,13 +5619,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1358</v>
+        <v>1545</v>
       </c>
       <c r="Q55" t="n">
-        <v>353</v>
+        <v>810</v>
       </c>
       <c r="R55" t="n">
-        <v>1711</v>
+        <v>2355</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5614,17 +5634,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1338314528</t>
+          <t>1538515183</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338314528</t>
+          <t>https://m.place.naver.com/place/1538515183</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5636,29 +5656,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>내안에봄의원 일산</t>
+          <t>일산고운세상피부과의원</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>naeanebom@naver.com</t>
+          <t>gwssskin@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1391-8576</t>
+          <t>031-932-8275</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 33 벨라시타 쇼핑몰 1층 1102호 내안에봄의원 일산</t>
+          <t>경기도 고양시 일산동구 정발산로 47 웅신아트 4층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://youtube.com/@pibuunnie</t>
+          <t>http://www.gowoonss.com/ilsan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5689,17 +5709,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>651</v>
+        <v>401</v>
       </c>
       <c r="Q56" t="n">
-        <v>1481</v>
+        <v>631</v>
       </c>
       <c r="R56" t="n">
-        <v>2132</v>
+        <v>1032</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5708,17 +5728,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>13584814</t>
+          <t>13096274</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13584814</t>
+          <t>https://m.place.naver.com/place/13096274</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5730,29 +5750,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>일산이지함피부과의원</t>
+          <t>수피부과의원 파주운정점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>argecjd6260@naver.com</t>
+          <t>pajusooskin@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1490-5301</t>
+          <t>0507-1449-0506</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1413 4층 이지함피부과</t>
+          <t>경기도 파주시 미래로 371 씨티타워 3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/argecjd6260</t>
+          <t>https://www.instagram.com/sooskin2014/?next=%2F</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5767,7 +5787,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5783,17 +5803,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>428</v>
+        <v>1494</v>
       </c>
       <c r="Q57" t="n">
-        <v>52</v>
+        <v>1701</v>
       </c>
       <c r="R57" t="n">
-        <v>480</v>
+        <v>3195</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5802,17 +5822,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>20038099</t>
+          <t>35003670</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20038099</t>
+          <t>https://m.place.naver.com/place/35003670</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5824,34 +5844,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>오킴스피부과의원</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ohkims123456@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티온의원 파주운정점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1481-9335</t>
+          <t>0507-1375-8428</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 123 뉴삼창빌딩 10층</t>
+          <t>경기도 파주시 경의로 1068 7층 702호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.ohkimsskin.com/</t>
+          <t>https://paju.beautyon.co.kr/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5861,7 +5877,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5877,17 +5893,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>915</v>
+        <v>1078</v>
       </c>
       <c r="Q58" t="n">
-        <v>41</v>
+        <v>2050</v>
       </c>
       <c r="R58" t="n">
-        <v>956</v>
+        <v>3128</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5896,17 +5912,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>12776434</t>
+          <t>1997387146</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12776434</t>
+          <t>https://m.place.naver.com/place/1997387146</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5918,29 +5934,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>수피부과의원 파주운정점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>pajusooskin@naver.com</t>
-        </is>
-      </c>
+          <t>유진피부과의원</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1449-0506</t>
+          <t>031-917-6749</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 파주시 미래로 371 씨티타워 3층</t>
+          <t>경기도 고양시 일산서구 강선로 59 동신파크빌딩</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sooskin2014/?next=%2F</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5950,7 +5962,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5971,17 +5983,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1492</v>
+        <v>518</v>
       </c>
       <c r="Q59" t="n">
-        <v>1630</v>
+        <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>3122</v>
+        <v>524</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5990,17 +6002,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>35003670</t>
+          <t>13237201</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35003670</t>
+          <t>https://m.place.naver.com/place/13237201</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6012,33 +6024,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>메이린의원 일산</t>
+          <t>사적인 아름다움 지유의원 일산점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>alawpearson@naver.com</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>mkt@maylin.co.kr</t>
-        </is>
-      </c>
+          <t>rkawjs1891@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1393-0000</t>
+          <t>031-812-0196</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 현대백화점 킨텍스점 9층 메이린클리닉</t>
+          <t>경기도 고양시 일산동구 정발산로 21 501호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.maylin.co.kr/ilsan/</t>
+          <t>https://ilsan.gu.clinic/kr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6048,12 +6056,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6064,7 +6072,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6073,13 +6081,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>69</v>
+        <v>3370</v>
       </c>
       <c r="Q60" t="n">
-        <v>342</v>
+        <v>3044</v>
       </c>
       <c r="R60" t="n">
-        <v>411</v>
+        <v>6414</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6088,17 +6096,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>19534963</t>
+          <t>1686302028</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19534963</t>
+          <t>https://m.place.naver.com/place/1686302028</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6110,24 +6118,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>벨피부과의원</t>
+          <t>일산의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>honma2005@naver.com</t>
+          <t>medi114_official@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>031-902-4320</t>
+          <t>031-976-1240</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 경의로 315 설촌상가</t>
+          <t>경기도 고양시 일산서구 고양대로 691</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6167,13 +6175,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>320</v>
+        <v>206</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6182,17 +6190,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13236957</t>
+          <t>13237890</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13236957</t>
+          <t>https://m.place.naver.com/place/13237890</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6204,25 +6212,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>최병문피부과의원</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>스카이비뇨의학과의원</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>skyuroskin@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>031-965-5800</t>
+          <t>031-813-7582</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 호국로 787 원당메디컬프라자</t>
+          <t>경기도 고양시 일산동구 숲속마을1로 73 신성메디칼타운 601호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/skyuroskin</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6232,12 +6244,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6257,13 +6269,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>977</v>
+        <v>412</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="R62" t="n">
-        <v>995</v>
+        <v>444</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6272,17 +6284,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>13237675</t>
+          <t>1050410147</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13237675</t>
+          <t>https://m.place.naver.com/place/1050410147</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6294,38 +6306,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>클린업피부과의원 일산</t>
+          <t>파크뷰의원 운정점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cleanup-is@naver.com</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>promotion@cunetwork.co.kr</t>
-        </is>
-      </c>
+          <t>thdwjdals25@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1402-1877</t>
+          <t>031-939-1100</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1420 진영빌딩 5층</t>
+          <t>경기도 파주시 와석순환로 507 월드타워9차 6층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.upskin.co.kr/index_is.php?introClass=3&amp;introBranch=0</t>
+          <t>http://pskin.kr/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6346,7 +6354,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6355,13 +6363,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1023</v>
+        <v>1139</v>
       </c>
       <c r="Q63" t="n">
-        <v>695</v>
+        <v>1963</v>
       </c>
       <c r="R63" t="n">
-        <v>1718</v>
+        <v>3102</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6370,17 +6378,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>11874651</t>
+          <t>33021543</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11874651</t>
+          <t>https://m.place.naver.com/place/33021543</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6392,29 +6400,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>예안의원</t>
+          <t>뷰티안의원</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>parknohsang@naver.com</t>
+          <t>objms@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>031-977-7579</t>
+          <t>0507-1396-2816</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 씨티프라자</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타D 221호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.yeanclinic.com/</t>
+          <t>https://blog.naver.com/objms</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6429,7 +6437,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6449,13 +6457,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>492</v>
+        <v>9</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>498</v>
+        <v>12</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6464,17 +6472,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>12063319</t>
+          <t>1398931993</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12063319</t>
+          <t>https://m.place.naver.com/place/1398931993</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6486,29 +6494,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>온봄의원</t>
+          <t>유앤아이의원 일산점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>onbom_clinic@naver.com</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>chiritachi197244@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mdvision@nate.com</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1323-0075</t>
+          <t>031-994-6021</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 45 C동 2층 218호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 38-5 이레21빌딩 4층 401, 402, 403호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://www.onbomclinic.co.kr</t>
+          <t>https://www.isuni114.co.kr/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6518,7 +6530,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6534,7 +6546,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6543,13 +6555,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>249</v>
+        <v>801</v>
       </c>
       <c r="Q65" t="n">
-        <v>29</v>
+        <v>5016</v>
       </c>
       <c r="R65" t="n">
-        <v>278</v>
+        <v>5817</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6558,17 +6570,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1303562689</t>
+          <t>1143822491</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303562689</t>
+          <t>https://m.place.naver.com/place/1143822491</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6580,30 +6592,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>베스트미의원</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>밴스의원 일산</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>vandsis@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>031-907-3375</t>
+          <t>031-994-0380</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 229 글로리코아 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 6층 601, 603호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://ilsan.vandsclinic.co.kr/?channel=1687</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6613,7 +6629,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6624,22 +6640,22 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>167</v>
+        <v>1391</v>
       </c>
       <c r="Q66" t="n">
-        <v>110</v>
+        <v>3611</v>
       </c>
       <c r="R66" t="n">
-        <v>277</v>
+        <v>5002</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6648,17 +6664,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1084521027</t>
+          <t>1481200696</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1084521027</t>
+          <t>https://m.place.naver.com/place/1481200696</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6727,13 +6743,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q67" t="n">
         <v>49</v>
       </c>
       <c r="R67" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6752,7 +6768,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6764,33 +6780,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>미앤미의원 일산</t>
+          <t>스타필의원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abte1954@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>webtick@gmail.com</t>
-        </is>
-      </c>
+          <t>miandmo@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1411-8941</t>
+          <t>031-965-2255</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 8층 미앤미의원 일산</t>
+          <t>경기도 고양시 덕양구 호국로789번길 6 중앙빌딩 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://is.mipretty.co.kr/</t>
+          <t>https://blog.naver.com/miandmo</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6800,7 +6812,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6816,22 +6828,22 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>592</v>
+        <v>273</v>
       </c>
       <c r="Q68" t="n">
-        <v>3399</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>3991</v>
+        <v>277</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6840,17 +6852,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>35135661</t>
+          <t>20367149</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35135661</t>
+          <t>https://m.place.naver.com/place/20367149</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6862,29 +6874,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>메이에버의원</t>
+          <t>리버스의원 일산</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2000kih@naver.com</t>
+          <t>dbsvlfwns1@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>031-983-6758</t>
+          <t>031-906-5555</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 250 골든타임 5층 메이에버의원</t>
+          <t>경기도 고양시 일산동구 정발산로 23 호수빌딩 502호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://mayever.co.kr/</t>
+          <t>https://is.reverseclinic.com</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6899,7 +6911,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6910,22 +6922,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>273</v>
+        <v>753</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>2239</v>
       </c>
       <c r="R69" t="n">
-        <v>307</v>
+        <v>2992</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6934,17 +6946,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1027733049</t>
+          <t>34508126</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027733049</t>
+          <t>https://m.place.naver.com/place/34508126</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6956,39 +6968,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>메이퓨어의원 일산점</t>
+          <t>주엽 제일의원</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jh9003__@naver.com</t>
+          <t>ske703@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>031-923-3196</t>
+          <t>031-918-8118</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 3층 301호</t>
+          <t>경기도 고양시 일산서구 중앙로 1437 화성프라자</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.maypureclinic.com/ko/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7004,22 +7016,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>830</v>
+        <v>173</v>
       </c>
       <c r="Q70" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1287</v>
+        <v>173</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7028,17 +7040,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1598670753</t>
+          <t>13237231</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598670753</t>
+          <t>https://m.place.naver.com/place/13237231</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7050,39 +7062,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>델타피부과의원</t>
+          <t>예쁨톡톡의원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>tpdml02@naver.com</t>
+          <t>seasons0907@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1339-7565</t>
+          <t>031-943-5422</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 현대센트럴스퀘어 620호</t>
+          <t>경기도 파주시 초롱꽃로 109 4층 407호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://deltaclinic.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7107,13 +7119,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>414</v>
+        <v>219</v>
       </c>
       <c r="Q71" t="n">
-        <v>325</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>739</v>
+        <v>220</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7122,17 +7134,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1260275940</t>
+          <t>1919348740</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260275940</t>
+          <t>https://m.place.naver.com/place/1919348740</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7238,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7253,11 @@
           <t>성보의원</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>gokory@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -7316,7 +7332,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7426,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7441,11 @@
           <t>장항중앙의원</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dd0096@naver.com</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
@@ -7500,7 +7520,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7569,13 +7589,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="Q76" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="R76" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7594,7 +7614,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
